--- a/04_extract_results/auto_pathway_matches.xlsx
+++ b/04_extract_results/auto_pathway_matches.xlsx
@@ -541,16 +541,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pathway; COCO</t>
+          <t>pathway; COCO; operando</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -657,16 +657,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ethanol; HCOO</t>
+          <t>ethanol; HCOO; spectroscopy</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>product_terms; pathway_terms</t>
+          <t>product_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -758,31 +758,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29035-8 Density functional theory calculations.</t>
+          <t>CO molecules interact with two exposed Cu atoms, result suggested the rate-determining steps (RDS) altered when 2 respectively, forming coadsorbed (*OCHO+*OCHO) (State 3). thepotentialatdecreasedto−1.2Vvs.RHE,combiningtheFTIR One adsorbed *OCHO was firstly reduced to form *CH +* results in Fig. 4d.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Theoretical investigabondformationtoCH CH OH.Similarreactionprocessesbased 3 2 tions were conducted based on DFT calculations to further on *OCHO mechanism were considered for Cu –CuN , as well 3 3 understand the reaction mechanism of the Cu –CuN cluster asCuN andCu–CuN whichcontainedonlyoneactiveCusite, 2 3 3 3 withCH * adsorbed.AsupportedCu –CuN clustermodelwith as shownin Supplementary Fig. 29.Thecalculated overpotential 3 2 3 aCubondingwiththreeNatomsonN-dopedcarbonnanosheets (−0.501V) for Cu –CuN cluster was much lower than that of 2 3 was proposed to be the structure of active sites with an applied CuN (−1.685V), Cu–CuN (−1.368V) and Cu –CuN 3 3 3 3 potential of −1.1V vs.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>RHE in Supplementary Fig. 28a.</t>
-        </is>
-      </c>
+          <t>To further analysis why RDS changed during 3 OCHO (State 9), and then the other *OCHO was reduced to the reaction, the different charge density for Cu -CuN (with/ 2 3 construct*CH +*OCH (State12),thatwentthroughtheC–C without CH * ) and Cu -CuN (with/without CH * ) was 3 2 3 3 3 3 Fig.5DFTcalculationsofCO RRactivity.aReactionprogressofCO toCH CH OHontheCu –CuN at0Vand−0.501Vappliedpotential.The* 2 2 3 2 2 3 showedthereactionsite.Thestatewiththehighestenergybarrier(0.501eV)is8→9.Allstatesinvolvingthetransferofthe(H++e−)pairwere electrochemicalreactionstates,exceptforthe12→13state(CH *+OCH *→OCH CH *),whichwastheC–Cbondformationandnotinfluencedby 3 2 2 3 appliedpotential.bLocalstructuresoftheactivesiteandintermediatestate.Theballsinbrown,blue,red,grayandwhiterepresentCu,N,O,C,andH atoms,respectively. 8 NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>mechanism; CHO; OCHO</t>
+          <t>intermediate; CHO; OCHO; DFT; barrier; calculation; calculations</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -816,31 +812,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>It corresponded Fig. 28, and Supplementary Data 1–1352.</t>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29035-8 Density functional theory calculations.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The *OCHO mechanwiththecompetingreactionofH andCH increasingwhenthe 2 4 ism was preferred for our catalysts than the *CO mechanisms, potential decreased.</t>
+          <t>Theoretical investigabondformationtoCH CH OH.Similarreactionprocessesbased 3 2 tions were conducted based on DFT calculations to further on *OCHO mechanism were considered for Cu –CuN , as well 3 3 understand the reaction mechanism of the Cu –CuN cluster asCuN andCu–CuN whichcontainedonlyoneactiveCusite, 2 3 3 3 withCH * adsorbed.AsupportedCu –CuN clustermodelwith as shownin Supplementary Fig. 29.Thecalculated overpotential 3 2 3 aCubondingwiththreeNatomsonN-dopedcarbonnanosheets (−0.501V) for Cu –CuN cluster was much lower than that of 2 3 was proposed to be the structure of active sites with an applied CuN (−1.685V), Cu–CuN (−1.368V) and Cu –CuN 3 3 3 3 potential of −1.1V vs.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>* due to the production of CO was suppressed along with the CH 3 was the key intermediate for C 2+formation rates and it formation ofethanol atthepotentials below−0.8Vas shownin occurred when the potential decreased to −0.6V vs.</t>
+          <t>RHE in Supplementary Fig. 28a.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>mechanism; CHO; OCHO</t>
+          <t>mechanism; CHO; OCHO; DFT; calculation; calculations</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -889,16 +885,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rate-determining; CHO; OCHO</t>
+          <t>rate-determining; CHO; OCHO; FTIR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -932,18 +928,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CO molecules interact with two exposed Cu atoms, result suggested the rate-determining steps (RDS) altered when 2 respectively, forming coadsorbed (*OCHO+*OCHO) (State 3). thepotentialatdecreasedto−1.2Vvs.RHE,combiningtheFTIR One adsorbed *OCHO was firstly reduced to form *CH +* results in Fig. 4d.</t>
+          <t>It corresponded Fig. 28, and Supplementary Data 1–1352.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>To further analysis why RDS changed during 3 OCHO (State 9), and then the other *OCHO was reduced to the reaction, the different charge density for Cu -CuN (with/ 2 3 construct*CH +*OCH (State12),thatwentthroughtheC–C without CH * ) and Cu -CuN (with/without CH * ) was 3 2 3 3 3 3 Fig.5DFTcalculationsofCO RRactivity.aReactionprogressofCO toCH CH OHontheCu –CuN at0Vand−0.501Vappliedpotential.The* 2 2 3 2 2 3 showedthereactionsite.Thestatewiththehighestenergybarrier(0.501eV)is8→9.Allstatesinvolvingthetransferofthe(H++e−)pairwere electrochemicalreactionstates,exceptforthe12→13state(CH *+OCH *→OCH CH *),whichwastheC–Cbondformationandnotinfluencedby 3 2 2 3 appliedpotential.bLocalstructuresoftheactivesiteandintermediatestate.Theballsinbrown,blue,red,grayandwhiterepresentCu,N,O,C,andH atoms,respectively. 8 NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>The *OCHO mechanwiththecompetingreactionofH andCH increasingwhenthe 2 4 ism was preferred for our catalysts than the *CO mechanisms, potential decreased.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>* due to the production of CO was suppressed along with the CH 3 was the key intermediate for C 2+formation rates and it formation ofethanol atthepotentials below−0.8Vas shownin occurred when the potential decreased to −0.6V vs.</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>intermediate; CHO; OCHO</t>
+          <t>mechanism; CHO; OCHO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -997,16 +997,16 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>intermediate; C–C coupling; coupling; CHO; OCHO</t>
+          <t>intermediate; C–C coupling; coupling; CHO; OCHO; in situ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1113,16 +1113,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>dimerization; CO dimerization</t>
+          <t>dimerization; CO dimerization; energy barrier; barrier</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>coupling_terms</t>
+          <t>coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1960,31 +1960,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Figure 3e and Extended data Fig. 48 show that the methyl C 1 (*CH ) in ethanol comes from HCOOH, while the C in CO goes to the methylene C (*CH OH).</t>
+          <t>The differential charge distribution analysis and Bader charges of 3 determined that the positive charge was higher on the Sn atom, such that bonding between Sn atom and HCOOH (externally added or in-situ produced over SnS ) was favored.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
+          <t>With PCET, the carbonyl group in HCOOH* can easily dehydrate to 2 generate Sn-CHO in intermediate 4, with a free energy barrier of 0.52 eV.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Extensive DFT calculations were performed using the computational hydrogen electrode (CHE) model 22,23,24,25 to map the CO RR pathway and energetics during the formation of ethanol.</t>
+          <t>This intermediate 4 features *CHO on Sn and *CO(OH) on the neighboring O (i.e., O2Sn-O-CO(OH) bicarbonate), which explains the activities of Sn and O atoms as the dual active centers in the Sn -O3G.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ethanol; rate-determining; HCOO</t>
+          <t>intermediate; CHO; HCOO; free energy; energy barrier; barrier</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2018,31 +2018,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The differential charge distribution analysis and Bader charges of 3 determined that the positive charge was higher on the Sn atom, such that bonding between Sn atom and HCOOH (externally added or in-situ produced over SnS ) was favored.</t>
+          <t>Figure 3e and Extended data Fig. 48 show that the methyl C 1 (*CH ) in ethanol comes from HCOOH, while the C in CO goes to the methylene C (*CH OH).</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>With PCET, the carbonyl group in HCOOH* can easily dehydrate to 2 generate Sn-CHO in intermediate 4, with a free energy barrier of 0.52 eV.</t>
+          <t>Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>This intermediate 4 features *CHO on Sn and *CO(OH) on the neighboring O (i.e., O2Sn-O-CO(OH) bicarbonate), which explains the activities of Sn and O atoms as the dual active centers in the Sn -O3G.</t>
+          <t>Extensive DFT calculations were performed using the computational hydrogen electrode (CHE) model 22,23,24,25 to map the CO RR pathway and energetics during the formation of ethanol.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>intermediate; CHO; HCOO</t>
+          <t>ethanol; rate-determining; HCOO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; pathway_terms</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2373,16 +2373,16 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>COCO; spectroscopy</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>oxygenate; C–C coupling; coupling; OCCO; COH</t>
+          <t>oxygenate; C–C coupling; coupling; OCCO; COH; calculation</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>product_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2779,16 +2779,16 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ethanol; pathway; intermediate; COCO</t>
+          <t>ethanol; pathway; intermediate; COCO; in situ; spectroscopy</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2837,16 +2837,16 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>COCO; Raman</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>intermediate; coupling; OCCO; CHO; COH</t>
+          <t>intermediate; coupling; OCCO; CHO; COH; barrier</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3401,16 +3401,16 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>pathway; OCCO</t>
+          <t>pathway; OCCO; adsorption energy</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3691,16 +3691,16 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ethanol; dimerization; CO dimerization</t>
+          <t>ethanol; dimerization; CO dimerization; in situ; Raman; spectroscopy</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>product_terms; coupling_terms</t>
+          <t>product_terms; coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3749,16 +3749,16 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; C–C coupling; coupling; HCOO</t>
+          <t>ethanol; intermediate; C–C coupling; coupling; HCOO; Raman</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>intermediate; OCCO</t>
+          <t>intermediate; OCCO; DFT; in situ; Raman</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3923,16 +3923,16 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; OCCO; COCO; CHO</t>
+          <t>ethanol; intermediate; OCCO; COCO; CHO; in situ; Raman</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>intermediate; OCCO; COCO; HCOO</t>
+          <t>intermediate; OCCO; COCO; HCOO; DFT; Raman</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4024,40 +4024,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21).</t>
+          <t>Raman spectra were achieved 2 fingerprints.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>As shown in Fig. 4c, similar bands at about 1,290 cm−1, 1,420 cm−1 COH, *OCCHOH, *CHO and *CH; Supplementary Tables 7–11), we attriband 1,605 cm−1 are observed during glyoxal reduction.</t>
+          <t>DFT vibrational frequencies for *CO2−, *COCO−, OCHCH (top, left by applying a smearing of 10 cm−1 on each DFT frequency and overlapping the 3 2 to right), *HCOOH, *OCOCO2− and *OCHCH (bottom, left to right) on adsorption resulting peaks.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>We attribute ute the 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 1,595 cm−1 signals detected the variations in relative intensities and positions to the substantially at −0.85 V and below to the CCO symmetric stretching, CCO antisymdifferent chemical environment in the absence of predominantly RHE metric stretching, C–C stretching and C–O (or C=C) stretching of co-adsorbed CO, as is the case in CORR.</t>
+          <t>Inset: different CORR reaction intermediates, with H atoms s 3 2 sites with different coordination numbers, increasing from orange to black. given in white, O atoms in red and C atoms in black.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CHO; COH</t>
+          <t>COCO; HCOO; DFT</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1;P5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>P2:*CHO</t>
+          <t>P1:*COCO; P1:COCO; P5:HCOO</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4082,40 +4082,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Raman spectra were achieved 2 fingerprints.</t>
+          <t>In Fig. 3, we show the main reaction intermediates responsible for Since similar C–C coupling intermediates were proposed for the vibrational frequencies detected experimentally (Fig. 2a).</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DFT vibrational frequencies for *CO2−, *COCO−, OCHCH (top, left by applying a smearing of 10 cm−1 on each DFT frequency and overlapping the 3 2 to right), *HCOOH, *OCOCO2− and *OCHCH (bottom, left to right) on adsorption resulting peaks.</t>
+          <t>After CORR3,38, to validate our observations, we performed in situ SERS the reduction of the Cu oxidic phases, *CO2− and *HCOO−/*HCOOH during CORR.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Inset: different CORR reaction intermediates, with H atoms s 3 2 sites with different coordination numbers, increasing from orange to black. given in white, O atoms in red and C atoms in black.</t>
+          <t>Our data show similar bands (Supplementary Fig. 18). 3 species form (see 1,070 cm−1, 1,390 cm−1 and 1,610 cm−1 signals in Fig. 3; We further prove the appearance of C–C coupling intermediates by Supplementary Tables 1–3).</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COCO; HCOO</t>
+          <t>HCOO; in situ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>P1:*COCO; P1:COCO; P5:HCOO</t>
+          <t>P5:HCOO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4140,22 +4140,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>In Fig. 3, we show the main reaction intermediates responsible for Since similar C–C coupling intermediates were proposed for the vibrational frequencies detected experimentally (Fig. 2a).</t>
+          <t>Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21).</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>After CORR3,38, to validate our observations, we performed in situ SERS the reduction of the Cu oxidic phases, *CO2− and *HCOO−/*HCOOH during CORR.</t>
+          <t>As shown in Fig. 4c, similar bands at about 1,290 cm−1, 1,420 cm−1 COH, *OCCHOH, *CHO and *CH; Supplementary Tables 7–11), we attriband 1,605 cm−1 are observed during glyoxal reduction.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Our data show similar bands (Supplementary Fig. 18). 3 species form (see 1,070 cm−1, 1,390 cm−1 and 1,610 cm−1 signals in Fig. 3; We further prove the appearance of C–C coupling intermediates by Supplementary Tables 1–3).</t>
+          <t>We attribute ute the 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 1,595 cm−1 signals detected the variations in relative intensities and positions to the substantially at −0.85 V and below to the CCO symmetric stretching, CCO antisymdifferent chemical environment in the absence of predominantly RHE metric stretching, C–C stretching and C–O (or C=C) stretching of co-adsorbed CO, as is the case in CORR.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HCOO</t>
+          <t>CHO; COH</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>P5:HCOO</t>
+          <t>P2:*CHO</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4383,16 +4383,16 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>intermediate; OCCO</t>
+          <t>intermediate; OCCO; Raman</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4656,38 +4656,42 @@
       <c r="C74" t="n">
         <v>8</v>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41560-024-01633-4 The hypothesis of OCCO(H) as a common C precursor for CO Methods 2+ 2 reduction is reinforced by the strong correlation between ethanol Electrode preparations and ethylene Faradaic efficiency on copper (R2 = 0.90, values taken A commercial polycrystalline copper foil (Advent Research Materials, from ref. 51; see Supplementary Fig. 26 and Supplementary Table 19). 99.995%) was used in all experiments.</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article https://doi.org/10.1038/s41560-024-01633-4 The hypothesis of OCCO(H) as a common C precursor for CO Methods 2+ 2 reduction is reinforced by the strong correlation between ethanol Electrode preparations and ethylene Faradaic efficiency on copper (R2 = 0.90, values taken A commercial polycrystalline copper foil (Advent Research Materials, from ref. 51; see Supplementary Fig. 26 and Supplementary Table 19). 99.995%) was used in all experiments.</t>
+          <t>Before each experiment, the copIn line with recent advances20, additional parallel pathways, such as per foil was electropolished at 3 V versus a titanium foil for 3 min in a CO–CH coupling (grey arrows, Fig. 7), may also open, yet our DFT HPO/HSO solution consisting of 130 ml HPO (VWR, 85 wt%), 20 ml x 3 4 2 4 3 4 simulations disprove any major role of these on distorted sites.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Before each experiment, the copIn line with recent advances20, additional parallel pathways, such as per foil was electropolished at 3 V versus a titanium foil for 3 min in a CO–CH coupling (grey arrows, Fig. 7), may also open, yet our DFT HPO/HSO solution consisting of 130 ml HPO (VWR, 85 wt%), 20 ml x 3 4 2 4 3 4 simulations disprove any major role of these on distorted sites.</t>
+          <t>In fact, HSO (VWR, 95%) and 60 ml ultrapure water.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ethanol; OCCO</t>
+          <t>pathway; coupling; DFT</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>product_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>P1:OCCO</t>
+          <t>P6:parallel pathway</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4710,29 +4714,25 @@
       <c r="C75" t="n">
         <v>8</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41560-024-01633-4 The hypothesis of OCCO(H) as a common C precursor for CO Methods 2+ 2 reduction is reinforced by the strong correlation between ethanol Electrode preparations and ethylene Faradaic efficiency on copper (R2 = 0.90, values taken A commercial polycrystalline copper foil (Advent Research Materials, from ref. 51; see Supplementary Fig. 26 and Supplementary Table 19). 99.995%) was used in all experiments.</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Before each experiment, the copIn line with recent advances20, additional parallel pathways, such as per foil was electropolished at 3 V versus a titanium foil for 3 min in a CO–CH coupling (grey arrows, Fig. 7), may also open, yet our DFT HPO/HSO solution consisting of 130 ml HPO (VWR, 85 wt%), 20 ml x 3 4 2 4 3 4 simulations disprove any major role of these on distorted sites.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>In fact, HSO (VWR, 95%) and 60 ml ultrapure water.</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>pathway; coupling</t>
+          <t>ethanol; OCCO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms</t>
+          <t>product_terms; pathway_terms</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>P6:parallel pathway</t>
+          <t>P1:OCCO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4781,16 +4781,16 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; pathway; intermediate; C-C coupling; coupling; CHO; COH</t>
+          <t>ethanol; mechanism; pathway; intermediate; C-C coupling; coupling; CHO; COH; operando; calculation</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4839,16 +4839,16 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HCOO</t>
+          <t>HCOO; DFT; barrier; operando; Raman; calculation; calculations; spectroscopy</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5071,16 +5071,16 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; coupling; COCO; CHO; OCHO</t>
+          <t>ethanol; intermediate; coupling; COCO; CHO; OCHO; DFT; barrier; operando; Raman; calculation; calculations; spectroscopy</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5245,16 +5245,16 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>intermediate; COCO</t>
+          <t>intermediate; COCO; Raman</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5357,16 +5357,16 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; intermediate; coupling; CHO; OCHO</t>
+          <t>ethanol; mechanism; intermediate; coupling; CHO; OCHO; DFT; calculation; calculations</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5411,16 +5411,16 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>pathway; intermediate; COCO; CHO; OCHO</t>
+          <t>pathway; intermediate; COCO; CHO; OCHO; DFT; operando; Raman</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5465,16 +5465,16 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; pathway; C-C coupling; coupling; COCO; CHO; COH</t>
+          <t>ethanol; mechanism; pathway; C-C coupling; coupling; COCO; CHO; COH; energy barrier; barrier; operando</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5519,16 +5519,16 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; pathway; CHO; COH</t>
+          <t>ethanol; mechanism; pathway; CHO; COH; DFT</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -5635,16 +5635,16 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ethanol; coupling; CHO</t>
+          <t>ethanol; coupling; CHO; barrier; calculation; calculations; spectroscopy</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>product_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5805,16 +5805,16 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>mechanism; intermediate; CHO</t>
+          <t>mechanism; intermediate; CHO; FTIR</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5917,16 +5917,16 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>intermediate; coupling; OCCO; COH</t>
+          <t>intermediate; coupling; OCCO; COH; FTIR</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5960,40 +5960,40 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>The 2 L C spectra recorded in a 12CO atmosphere with D O supported these views (Fig. 3d and 2 I T Supplementary Figure 60Rb, see details in Supplementary Note 1).</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Theoretical calculations of the A FTIR spectra of *OCCOH intermediates adsorbed on the surface of Co -Sub-CuS showed a 0.050 C=O stretching at 1151 cm-1, and a C-OH stretching at 1629 cm-1, which correspond to the experimental values of 1621 cm-1 and 1132 cm-1, respectively (Fig. 3e and Supplementary Fig. 61).</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Stronger bands at 1335 cm-1 and 1117 cm-1 were detected on Co -Sub-CuS, which are 0.050 attributed to *OC H 38,49,51-53, a key intermediate in EtOH production (Fig. 3a).</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>intermediate; coupling; OCCO</t>
+          <t>intermediate; OCCO; COH; FTIR; calculation; calculations</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1;P3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO</t>
+          <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6018,40 +6018,40 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The 2 L C spectra recorded in a 12CO atmosphere with D O supported these views (Fig. 3d and 2 I T Supplementary Figure 60Rb, see details in Supplementary Note 1).</t>
+          <t>Theoretical calculations of the A FTIR spectra of *OCCOH intermediates adsorbed on the surface of Co -Sub-CuS showed a 0.050 C=O stretching at 1151 cm-1, and a C-OH stretching at 1629 cm-1, which correspond to the experimental values of 1621 cm-1 and 1132 cm-1, respectively (Fig. 3e and Supplementary Fig. 61).</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Theoretical calculations of the A FTIR spectra of *OCCOH intermediates adsorbed on the surface of Co -Sub-CuS showed a 0.050 C=O stretching at 1151 cm-1, and a C-OH stretching at 1629 cm-1, which correspond to the experimental values of 1621 cm-1 and 1132 cm-1, respectively (Fig. 3e and Supplementary Fig. 61).</t>
+          <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
+          <t>Stronger bands at 1335 cm-1 and 1117 cm-1 were detected on Co -Sub-CuS, which are 0.050 attributed to *OC H 38,49,51-53, a key intermediate in EtOH production (Fig. 3a).</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>intermediate; OCCO; COH</t>
+          <t>intermediate; coupling; OCCO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>P1;P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
+          <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6547,16 +6547,16 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>pathway; coupling; OCCO; COH</t>
+          <t>pathway; coupling; OCCO; COH; barrier</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -6775,16 +6775,16 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCOO</t>
+          <t>HCOO; operando</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7061,16 +7061,16 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HCOO</t>
+          <t>HCOO; spectroscopy</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7119,16 +7119,16 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>intermediate; OCCO; CHO; COH</t>
+          <t>intermediate; OCCO; CHO; COH; Raman</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>intermediate; OCCO; CHO; COH</t>
+          <t>intermediate; OCCO; CHO; COH; Raman</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -7231,16 +7231,16 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C2H5OH; CHO; OCHO</t>
+          <t>C2H5OH; CHO; OCHO; DFT; Raman; calculation; calculations</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>product_terms; pathway_terms</t>
+          <t>product_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -7388,38 +7388,42 @@
       <c r="C122" t="n">
         <v>6</v>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c d e f Fig.4Computationalmodel.Representativestructuresof*COdimerizationatinitialstates(a),transitionstates(b),andfinalstates(c).Representative structuresof*COhydrogenationatinitialstates(d),transitionstates(e),andfinalstates(f). modes of *OH are compared with the Raman band observed ThisisconsistentwiththeobservedenhancementofC 2+product experimentally.</t>
+          <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
+          <t>Notably, these decreases are dimerization decrease as the *OH coverage increases from 0 to much more significant than those in *CO dimerization, which 3/9butreboundwithfurtherincreasein*OHcoverage(Fig.5a). agreeswiththesignificantanodicshiftofmethaneonsetpotential Boththeinitialstateandtransitionstatebecomelessstableasthe in the presence of the concurrent ORR (Fig. 2).</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>dimerization; COH</t>
+          <t>CHO; COH; DFT; free energy; barrier; calculation; calculations</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>coupling_terms; pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2;P3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>P3:*COH</t>
+          <t>P2:*CHO; P3:*COH</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7442,42 +7446,38 @@
       <c r="C123" t="n">
         <v>6</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c d e f Fig.4Computationalmodel.Representativestructuresof*COdimerizationatinitialstates(a),transitionstates(b),andfinalstates(c).Representative structuresof*COhydrogenationatinitialstates(d),transitionstates(e),andfinalstates(f). modes of *OH are compared with the Raman band observed ThisisconsistentwiththeobservedenhancementofC 2+product experimentally.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
-        </is>
-      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>dimerization; CO dimerization</t>
+          <t>dimerization; COH; Raman</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>coupling_terms</t>
+          <t>coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>P1:*CO dimerization; P1:CO dimerization</t>
+          <t>P3:*COH</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7502,40 +7502,40 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c d e f Fig.4Computationalmodel.Representativestructuresof*COdimerizationatinitialstates(a),transitionstates(b),andfinalstates(c).Representative structuresof*COhydrogenationatinitialstates(d),transitionstates(e),andfinalstates(f). modes of *OH are compared with the Raman band observed ThisisconsistentwiththeobservedenhancementofC 2+product experimentally.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Notably, these decreases are dimerization decrease as the *OH coverage increases from 0 to much more significant than those in *CO dimerization, which 3/9butreboundwithfurtherincreasein*OHcoverage(Fig.5a). agreeswiththesignificantanodicshiftofmethaneonsetpotential Boththeinitialstateandtransitionstatebecomelessstableasthe in the presence of the concurrent ORR (Fig. 2).</t>
-        </is>
-      </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CHO; COH</t>
+          <t>dimerization; CO dimerization; free energy; barrier; in situ; Raman</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>P2;P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>P2:*CHO; P3:*COH</t>
+          <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7633,16 +7633,16 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>dimerization; COH</t>
+          <t>dimerization; COH; barrier</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>coupling_terms; pathway_terms</t>
+          <t>coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -7687,16 +7687,16 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CHO; COH</t>
+          <t>CHO; COH; DFT; Raman; calculation; calculations; spectroscopy</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>dimerization; COH</t>
+          <t>dimerization; COH; barrier</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>coupling_terms; pathway_terms</t>
+          <t>coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -7861,16 +7861,16 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; coupling; CHO</t>
+          <t>ethanol; intermediate; coupling; CHO; DFT</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7977,16 +7977,16 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>pathway; C–C coupling; dimerization; CO dimerization; coupling; OCCO; COCO</t>
+          <t>pathway; C–C coupling; dimerization; CO dimerization; coupling; OCCO; COCO; DFT; barrier</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8147,16 +8147,16 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>intermediate; COCO</t>
+          <t>intermediate; COCO; adsorption energy</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -8263,16 +8263,16 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>dimerization; CO dimerization</t>
+          <t>dimerization; CO dimerization; calculation</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>coupling_terms</t>
+          <t>coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -8321,16 +8321,16 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>COCO; DFT; calculation</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -8433,16 +8433,16 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HCOO</t>
+          <t>HCOO; calculation; calculations</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -8545,16 +8545,16 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>dimerization; CO dimerization</t>
+          <t>dimerization; CO dimerization; in situ; spectroscopy</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>coupling_terms</t>
+          <t>coupling_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -8947,16 +8947,16 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; intermediate; coupling; OCCO; COH</t>
+          <t>ethanol; mechanism; intermediate; coupling; OCCO; COH; operando</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -9005,16 +9005,16 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; pathway; intermediate; coupling; OCCO; COH</t>
+          <t>ethanol; mechanism; pathway; intermediate; coupling; OCCO; COH; barrier; calculation</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -9121,16 +9121,16 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>pathway; intermediate; coupling; OCCO; COCO; COH</t>
+          <t>pathway; intermediate; coupling; OCCO; COCO; COH; free energy</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -9164,31 +9164,31 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
+          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
+          <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
+          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>pathway; intermediate; coupling; OCCO; COH</t>
+          <t>intermediate; C–C coupling; coupling; OCCO; COH; calculation; calculations</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -9222,31 +9222,31 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
+          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
+          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
+          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>intermediate; C–C coupling; coupling; OCCO; COH</t>
+          <t>pathway; intermediate; coupling; OCCO; COH; DFT</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9280,31 +9280,31 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>This step isthe potential-determine step (PDS) with a 2+ especially the alcohols.</t>
+          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
+          <t>(Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
+          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>pathway; intermediate; OCCO; COH</t>
+          <t>OCCO; COH; energy barrier; barrier; calculation; calculations</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO</t>
+          <t>P1:OCCO</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -9338,22 +9338,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
+          <t>This step isthe potential-determine step (PDS) with a 2+ especially the alcohols.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
+          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
+          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>mechanism; OCCO; COH</t>
+          <t>pathway; intermediate; OCCO; COH</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -9396,22 +9396,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
+          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>This is achieved betweentheCuclusterandadjacentsingleCucenteraffordsanextra 2 through the significantly enhanced *CO adsorption on the underO–Cu bond to stabilize the *OCCOH intermediate by breaking the coordinated sites.</t>
+          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte.</t>
+          <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>intermediate; OCCO; COH</t>
+          <t>mechanism; OCCO; COH</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>P1;P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
+          <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -9454,40 +9454,40 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
+          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
+          <t>This is achieved betweentheCuclusterandadjacentsingleCucenteraffordsanextra 2 through the significantly enhanced *CO adsorption on the underO–Cu bond to stabilize the *OCCOH intermediate by breaking the coordinated sites.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
+          <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>OCCO; COH</t>
+          <t>intermediate; OCCO; COH</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>pathway_terms</t>
+          <t>mechanism_terms; pathway_terms</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1;P3</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>P1:OCCO</t>
+          <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -9577,16 +9577,16 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ethanol; mechanism; pathway; intermediate; OCCO; COCO; CHO; COH; HCOO; CH2; CH3</t>
+          <t>ethanol; mechanism; pathway; intermediate; OCCO; COCO; CHO; COH; HCOO; CH2; CH3; DFT; barrier; calculation; calculations</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -9747,16 +9747,16 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>pathway; rate-determining; OCCO; COH</t>
+          <t>pathway; rate-determining; OCCO; COH; barrier</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>mechanism_terms; pathway_terms</t>
+          <t>mechanism_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9863,16 +9863,16 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>mechanism; coupling; COCO</t>
+          <t>mechanism; coupling; COCO; operando; Raman; FTIR; spectroscopy</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -10095,16 +10095,16 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; C–C coupling; coupling; CHO; COH</t>
+          <t>ethanol; intermediate; C–C coupling; coupling; CHO; COH; barrier</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -10138,40 +10138,40 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Simultaneously with the CO-related band, a band at residual Cl atoms61,62.</t>
+          <t>These effects stabilize the Fig. 32)48.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(2) The presence of coordination defects and 1305cm−1 associated with *COH stretching grows, and *COOH disoxygen vacancies increases the adsorption of intermediates rather appears in the spectra. which indicates the performance of CO than forming proton bonds with O atoms of Cu–O to avoid the 2 reduction.Theabsenceofthebandsat1589cm−1inthetransmission reductionofCu+species63,64.(3)Strongelectronicinteractionsoccur spectrapoints out the possibility of the *OCCOH coupling reaction betweencarbonintermediatesandCu+species65,66.WhenCOformsa duringthereductionofCO onCu /Cu O(Fig.5A).However,inconhybridizationorbitalwiththeCud-states,the5σand2π*orbitalsof*CO 2 L 2 trast to Cu /Cu O catalyst, some new signals at 1706, 1543, and splitintobondingandanti-bondingorbitals.Inthisprocess,electrons L 2 1399cm−1correspondingtothestretchof*CHO,*OCCO,and*OCHO fromtheCud-bandaretransferredtothe2πorbitalsof*COthroughdintermediatesemergedinspectraofCu /Cu O,certifyingthecoupling 2πbackdonation,whileelectronsfromthe5σorbitalof*COdonateto P 2 mode of OC–CO and possible formate product (Supplementary the Cu d-band through 5σ-d donation30.</t>
+          <t>Combining with time-independent spectral analysis (SupoxidationstateofCu+speciesduringCO electroreduction,allowing 2 plementaryFig.33A,B),apparentpeaksaredeterminedat1064and forthesynergisticeffectofCuandCu+species. 1558cm−1, which correspond well to the symmetric and asymmetric ThereactionbarriersforthehydrogenationprocessofC inter2+ vibrationsofthe*OCCOHintermediate,respectively49,50.Inaddition, mediatesonthemodelsofCu/CuOwithandwithoutCl,respectively, 2 thestretchingvibrationat1335and1716cm−1areincloseproximityto werecalculatedbyDFT.Firstly,byanalyzingtheBaderchargeandbond thestretchingof*OCH CH and*CHO,respectively,whichserveasthe length of Cu/CuO (Fig. 5C, D), it is observed that the lower Bader 2 3 L 2 important intermediates for the subsequent C–C coupling in the chargevalue(0.477|e|)comparedtoCu /CuO(1.01|e|)indicatesthat P 2 productionofC alcohols51,52.Theseconclusionsareconsistentwith thepopulatedelectronicorbitalsoflow-coordinatedCusiteswilleasily 2+ theresultsobtainedfromtheproductanalysisofCu /Cu OandCu / bindtointermediatesandreducetherate-determiningenergybarrier67.</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>These effects stabilize the Fig. 32)48.</t>
+          <t>P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>intermediate; coupling; OCCO; CHO; COH; OCHO; formate</t>
+          <t>intermediate; rate-determining; C–C coupling; coupling; OCCO; CHO; COH; DFT; barrier</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>P1;P2;P3;P5</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO; P2:*CHO; P3:*COH; P5:*OCHO; P5:OCHO</t>
+          <t>P1:*OCCO; P1:OCCO; P2:*CHO</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -10196,22 +10196,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>Simultaneously with the CO-related band, a band at residual Cl atoms61,62.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>(2) The presence of coordination defects and 1305cm−1 associated with *COH stretching grows, and *COOH disoxygen vacancies increases the adsorption of intermediates rather appears in the spectra. which indicates the performance of CO than forming proton bonds with O atoms of Cu–O to avoid the 2 reduction.Theabsenceofthebandsat1589cm−1inthetransmission reductionofCu+species63,64.(3)Strongelectronicinteractionsoccur spectrapoints out the possibility of the *OCCOH coupling reaction betweencarbonintermediatesandCu+species65,66.WhenCOformsa duringthereductionofCO onCu /Cu O(Fig.5A).However,inconhybridizationorbitalwiththeCud-states,the5σand2π*orbitalsof*CO 2 L 2 trast to Cu /Cu O catalyst, some new signals at 1706, 1543, and splitintobondingandanti-bondingorbitals.Inthisprocess,electrons L 2 1399cm−1correspondingtothestretchof*CHO,*OCCO,and*OCHO fromtheCud-bandaretransferredtothe2πorbitalsof*COthroughdintermediatesemergedinspectraofCu /Cu O,certifyingthecoupling 2πbackdonation,whileelectronsfromthe5σorbitalof*COdonateto P 2 mode of OC–CO and possible formate product (Supplementary the Cu d-band through 5σ-d donation30.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
           <t>These effects stabilize the Fig. 32)48.</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Combining with time-independent spectral analysis (SupoxidationstateofCu+speciesduringCO electroreduction,allowing 2 plementaryFig.33A,B),apparentpeaksaredeterminedat1064and forthesynergisticeffectofCuandCu+species. 1558cm−1, which correspond well to the symmetric and asymmetric ThereactionbarriersforthehydrogenationprocessofC inter2+ vibrationsofthe*OCCOHintermediate,respectively49,50.Inaddition, mediatesonthemodelsofCu/CuOwithandwithoutCl,respectively, 2 thestretchingvibrationat1335and1716cm−1areincloseproximityto werecalculatedbyDFT.Firstly,byanalyzingtheBaderchargeandbond thestretchingof*OCH CH and*CHO,respectively,whichserveasthe length of Cu/CuO (Fig. 5C, D), it is observed that the lower Bader 2 3 L 2 important intermediates for the subsequent C–C coupling in the chargevalue(0.477|e|)comparedtoCu /CuO(1.01|e|)indicatesthat P 2 productionofC alcohols51,52.Theseconclusionsareconsistentwith thepopulatedelectronicorbitalsoflow-coordinatedCusiteswilleasily 2+ theresultsobtainedfromtheproductanalysisofCu /Cu OandCu / bindtointermediatesandreducetherate-determiningenergybarrier67.</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55.</t>
-        </is>
-      </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>intermediate; rate-determining; C–C coupling; coupling; OCCO; CHO; COH</t>
+          <t>intermediate; coupling; OCCO; CHO; COH; OCHO; formate</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>P1;P2</t>
+          <t>P1;P2;P3;P5</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>P1:*OCCO; P1:OCCO; P2:*CHO</t>
+          <t>P1:*OCCO; P1:OCCO; P2:*CHO; P3:*COH; P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -10269,16 +10269,16 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>intermediate; coupling; COCO</t>
+          <t>intermediate; coupling; COCO; Raman</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10377,16 +10377,16 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ethanol; intermediate; coupling; COCO</t>
+          <t>ethanol; intermediate; coupling; COCO; DFT; operando; Raman; FTIR; calculation; calculations</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms</t>
+          <t>product_terms; mechanism_terms; coupling_terms; pathway_terms; evidence_terms</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
